--- a/Pennsylvania_NonMajority_Local2025.xlsx
+++ b/Pennsylvania_NonMajority_Local2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="124">
   <si>
     <t>Year</t>
   </si>
@@ -37,9 +37,6 @@
     <t>ADAMS SUPERVISOR Berwick</t>
   </si>
   <si>
-    <t>ALLEGHENY COMMISSIONER EAST DEER WARD 2</t>
-  </si>
-  <si>
     <t>ALLEGHENY COMMISSIONER ROBINSON</t>
   </si>
   <si>
@@ -55,12 +52,6 @@
     <t>BEAVER TAX COLLECTOR (4-YR) NEW SEWICKLEY TOWNSHIP</t>
   </si>
   <si>
-    <t>BERKS TOWNSHIP SUPERVISOR (6 YEAR) Brecknock Twp</t>
-  </si>
-  <si>
-    <t>BERKS TOWNSHIP SUPERVISOR Rockland Twp</t>
-  </si>
-  <si>
     <t>CUMBERLAND JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
@@ -79,9 +70,6 @@
     <t>DAUPHIN SUPERVISOR 6 YEAR TERM - DERRY</t>
   </si>
   <si>
-    <t>DAUPHIN SUSQUENITA SCHOOL DISTRICT III</t>
-  </si>
-  <si>
     <t>DELAWARE BETHEL TWP SUPERVISOR</t>
   </si>
   <si>
@@ -94,9 +82,6 @@
     <t>ERIE UNION TOWNSHIP SUPERVISOR</t>
   </si>
   <si>
-    <t>HUNTINGDON AUDITOR Springfield</t>
-  </si>
-  <si>
     <t>LACKAWANNA SUPERVISOR SOUTH ABINGTON</t>
   </si>
   <si>
@@ -136,12 +121,6 @@
     <t>CHRISTOPHER ADLER</t>
   </si>
   <si>
-    <t>ALEXANDER JAMES GIGLER</t>
-  </si>
-  <si>
-    <t>ED KISSEL</t>
-  </si>
-  <si>
     <t>KEN KISOW</t>
   </si>
   <si>
@@ -193,18 +172,6 @@
     <t>CANDRA SMITH</t>
   </si>
   <si>
-    <t>ANNETTE BAKER</t>
-  </si>
-  <si>
-    <t>RON MCCLURE WINNER BY DRAW</t>
-  </si>
-  <si>
-    <t>ERICKA THOMAS-ERNST WINNER BY DRAW</t>
-  </si>
-  <si>
-    <t>JANICE MCDERMOTT</t>
-  </si>
-  <si>
     <t>JODY SMITH</t>
   </si>
   <si>
@@ -271,12 +238,6 @@
     <t>DOMINIC GIOVANNIELLO</t>
   </si>
   <si>
-    <t>AMY RABIN</t>
-  </si>
-  <si>
-    <t>AMY REED</t>
-  </si>
-  <si>
     <t>STEPHANIE DEROHANNESSIAN</t>
   </si>
   <si>
@@ -320,12 +281,6 @@
   </si>
   <si>
     <t>GARY WELLS</t>
-  </si>
-  <si>
-    <t>GORDON BANKS LOCKE</t>
-  </si>
-  <si>
-    <t>KELLI DIANE GRISSINGER</t>
   </si>
   <si>
     <t>JOHN HAMBROSE</t>
@@ -788,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -819,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>316</v>
@@ -828,7 +783,7 @@
         <v>33.79679144385027</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -839,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>315</v>
@@ -848,7 +803,7 @@
         <v>33.68983957219251</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -859,7 +814,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>304</v>
@@ -868,7 +823,7 @@
         <v>32.51336898395722</v>
       </c>
       <c r="F4" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -879,16 +834,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>131</v>
+        <v>3573</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>35.77650946230099</v>
       </c>
       <c r="F6" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -899,36 +854,36 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>131</v>
+        <v>3254</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>32.58235706418343</v>
       </c>
       <c r="F7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>2025</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9">
-        <v>3573</v>
-      </c>
-      <c r="E9">
-        <v>35.77650946230099</v>
-      </c>
-      <c r="F9" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>3160</v>
+      </c>
+      <c r="E8">
+        <v>31.64113347351557</v>
+      </c>
+      <c r="F8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -939,16 +894,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D10">
-        <v>3254</v>
+        <v>4162</v>
       </c>
       <c r="E10">
-        <v>32.58235706418343</v>
+        <v>27.57021727609963</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -959,16 +914,36 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>3160</v>
+        <v>3939</v>
       </c>
       <c r="E11">
-        <v>31.64113347351557</v>
+        <v>26.09300476947536</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12">
+        <v>3564</v>
+      </c>
+      <c r="E12">
+        <v>23.60890302066773</v>
+      </c>
+      <c r="F12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -976,39 +951,19 @@
         <v>2025</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D13">
-        <v>4162</v>
+        <v>3431</v>
       </c>
       <c r="E13">
-        <v>27.57021727609963</v>
+        <v>22.72787493375728</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>2025</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14">
-        <v>3939</v>
-      </c>
-      <c r="E14">
-        <v>26.09300476947536</v>
-      </c>
-      <c r="F14" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1019,16 +974,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D15">
-        <v>3564</v>
+        <v>2207</v>
       </c>
       <c r="E15">
-        <v>23.60890302066773</v>
+        <v>27.22338719625015</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1039,16 +994,36 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D16">
-        <v>3431</v>
+        <v>2056</v>
       </c>
       <c r="E16">
-        <v>22.72787493375728</v>
+        <v>25.36079930923893</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>1946</v>
+      </c>
+      <c r="E17">
+        <v>24.00394720611817</v>
+      </c>
+      <c r="F17" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1056,39 +1031,19 @@
         <v>2025</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D18">
-        <v>2207</v>
+        <v>1898</v>
       </c>
       <c r="E18">
-        <v>27.22338719625015</v>
+        <v>23.41186628839275</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>2025</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19">
-        <v>2056</v>
-      </c>
-      <c r="E19">
-        <v>25.36079930923893</v>
-      </c>
-      <c r="F19" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1099,16 +1054,16 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>1946</v>
+        <v>559</v>
       </c>
       <c r="E20">
-        <v>24.00394720611817</v>
+        <v>46.62218515429525</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1119,36 +1074,36 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D21">
-        <v>1898</v>
+        <v>395</v>
       </c>
       <c r="E21">
-        <v>23.41186628839275</v>
+        <v>32.9441201000834</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>2025</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23">
-        <v>559</v>
-      </c>
-      <c r="E23">
-        <v>46.62218515429525</v>
-      </c>
-      <c r="F23" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22">
+        <v>245</v>
+      </c>
+      <c r="E22">
+        <v>20.43369474562135</v>
+      </c>
+      <c r="F22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1159,16 +1114,16 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>395</v>
+        <v>2212</v>
       </c>
       <c r="E24">
-        <v>32.9441201000834</v>
+        <v>37.94168096054889</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1179,36 +1134,36 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>245</v>
+        <v>1819</v>
       </c>
       <c r="E25">
-        <v>20.43369474562135</v>
+        <v>31.20068610634648</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>2025</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27">
-        <v>2212</v>
-      </c>
-      <c r="E27">
-        <v>37.94168096054889</v>
-      </c>
-      <c r="F27" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>1799</v>
+      </c>
+      <c r="E26">
+        <v>30.85763293310463</v>
+      </c>
+      <c r="F26" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1219,16 +1174,16 @@
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D28">
-        <v>1819</v>
+        <v>52340</v>
       </c>
       <c r="E28">
-        <v>31.20068610634648</v>
+        <v>39.71078048299356</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1239,36 +1194,36 @@
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D29">
-        <v>1799</v>
+        <v>40566</v>
       </c>
       <c r="E29">
-        <v>30.85763293310463</v>
+        <v>30.77775164449974</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>2025</v>
-      </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31">
-        <v>770</v>
-      </c>
-      <c r="E31">
-        <v>50</v>
-      </c>
-      <c r="F31" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30">
+        <v>38897</v>
+      </c>
+      <c r="E30">
+        <v>29.5114678725067</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1279,16 +1234,36 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D32">
-        <v>770</v>
+        <v>7166</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>27.76013016192764</v>
       </c>
       <c r="F32" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>2025</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33">
+        <v>6976</v>
+      </c>
+      <c r="E33">
+        <v>27.02409545208027</v>
+      </c>
+      <c r="F33" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1296,19 +1271,19 @@
         <v>2025</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D34">
-        <v>649</v>
+        <v>5878</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>22.77058960254126</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1316,19 +1291,19 @@
         <v>2025</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D35">
-        <v>649</v>
+        <v>5794</v>
       </c>
       <c r="E35">
-        <v>50</v>
+        <v>22.44518478345084</v>
       </c>
       <c r="F35" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1336,19 +1311,19 @@
         <v>2025</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D37">
-        <v>52340</v>
+        <v>80920</v>
       </c>
       <c r="E37">
-        <v>39.71078048299356</v>
+        <v>27.35243812575632</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1356,19 +1331,19 @@
         <v>2025</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D38">
-        <v>40566</v>
+        <v>78768</v>
       </c>
       <c r="E38">
-        <v>30.77775164449974</v>
+        <v>26.62502281623299</v>
       </c>
       <c r="F38" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1376,39 +1351,39 @@
         <v>2025</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D39">
-        <v>38897</v>
+        <v>69638</v>
       </c>
       <c r="E39">
-        <v>29.5114678725067</v>
+        <v>23.53891604302297</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>2025</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41">
-        <v>7166</v>
-      </c>
-      <c r="E41">
-        <v>27.76013016192764</v>
-      </c>
-      <c r="F41" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>2025</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40">
+        <v>66516</v>
+      </c>
+      <c r="E40">
+        <v>22.48362301498773</v>
+      </c>
+      <c r="F40" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1416,19 +1391,19 @@
         <v>2025</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D42">
-        <v>6976</v>
+        <v>2358</v>
       </c>
       <c r="E42">
-        <v>27.02409545208027</v>
+        <v>38.36641718190693</v>
       </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1436,19 +1411,19 @@
         <v>2025</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D43">
-        <v>5878</v>
+        <v>1956</v>
       </c>
       <c r="E43">
-        <v>22.77058960254126</v>
+        <v>31.8255776114546</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1456,19 +1431,19 @@
         <v>2025</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D44">
-        <v>5794</v>
+        <v>1832</v>
       </c>
       <c r="E44">
-        <v>22.44518478345084</v>
+        <v>29.80800520663847</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1476,19 +1451,19 @@
         <v>2025</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D46">
-        <v>80920</v>
+        <v>18394</v>
       </c>
       <c r="E46">
-        <v>27.35243812575632</v>
+        <v>28.40508987584162</v>
       </c>
       <c r="F46" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1496,19 +1471,19 @@
         <v>2025</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D47">
-        <v>78768</v>
+        <v>17852</v>
       </c>
       <c r="E47">
-        <v>26.62502281623299</v>
+        <v>27.56810179751683</v>
       </c>
       <c r="F47" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1516,19 +1491,19 @@
         <v>2025</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D48">
-        <v>69638</v>
+        <v>14556</v>
       </c>
       <c r="E48">
-        <v>23.53891604302297</v>
+        <v>22.47822595589598</v>
       </c>
       <c r="F48" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1536,19 +1511,19 @@
         <v>2025</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D49">
-        <v>66516</v>
+        <v>13954</v>
       </c>
       <c r="E49">
-        <v>22.48362301498773</v>
+        <v>21.54858237074557</v>
       </c>
       <c r="F49" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1556,19 +1531,19 @@
         <v>2025</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D51">
-        <v>2358</v>
+        <v>9620</v>
       </c>
       <c r="E51">
-        <v>38.36641718190693</v>
+        <v>30.37383177570093</v>
       </c>
       <c r="F51" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1576,19 +1551,19 @@
         <v>2025</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D52">
-        <v>1956</v>
+        <v>8774</v>
       </c>
       <c r="E52">
-        <v>31.8255776114546</v>
+        <v>27.7027027027027</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1596,39 +1571,39 @@
         <v>2025</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D53">
-        <v>1832</v>
+        <v>6746</v>
       </c>
       <c r="E53">
-        <v>29.80800520663847</v>
+        <v>21.29957059863602</v>
       </c>
       <c r="F53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>2025</v>
-      </c>
-      <c r="B55" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" t="s">
-        <v>77</v>
-      </c>
-      <c r="D55">
-        <v>18394</v>
-      </c>
-      <c r="E55">
-        <v>28.40508987584162</v>
-      </c>
-      <c r="F55" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>2025</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54">
+        <v>6532</v>
+      </c>
+      <c r="E54">
+        <v>20.62389492296034</v>
+      </c>
+      <c r="F54" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1636,19 +1611,19 @@
         <v>2025</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D56">
-        <v>17852</v>
+        <v>2085</v>
       </c>
       <c r="E56">
-        <v>27.56810179751683</v>
+        <v>28.31726198560369</v>
       </c>
       <c r="F56" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1656,19 +1631,19 @@
         <v>2025</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D57">
-        <v>14556</v>
+        <v>1975</v>
       </c>
       <c r="E57">
-        <v>22.47822595589598</v>
+        <v>26.82330571777808</v>
       </c>
       <c r="F57" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1676,39 +1651,39 @@
         <v>2025</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D58">
-        <v>13954</v>
+        <v>1703</v>
       </c>
       <c r="E58">
-        <v>21.54858237074557</v>
+        <v>23.12915931006383</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>2025</v>
-      </c>
-      <c r="B60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60">
-        <v>9620</v>
-      </c>
-      <c r="E60">
-        <v>30.37383177570093</v>
-      </c>
-      <c r="F60" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>2025</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59">
+        <v>1600</v>
+      </c>
+      <c r="E59">
+        <v>21.73027298655439</v>
+      </c>
+      <c r="F59" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1716,19 +1691,19 @@
         <v>2025</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D61">
-        <v>8774</v>
+        <v>119488</v>
       </c>
       <c r="E61">
-        <v>27.7027027027027</v>
+        <v>35.08326873840227</v>
       </c>
       <c r="F61" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1736,19 +1711,19 @@
         <v>2025</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D62">
-        <v>6746</v>
+        <v>107081</v>
       </c>
       <c r="E62">
-        <v>21.29957059863602</v>
+        <v>31.4404082399643</v>
       </c>
       <c r="F62" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1756,39 +1731,39 @@
         <v>2025</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D63">
-        <v>6532</v>
+        <v>57865</v>
       </c>
       <c r="E63">
-        <v>20.62389492296034</v>
+        <v>16.98993493528762</v>
       </c>
       <c r="F63" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>2025</v>
-      </c>
-      <c r="B65" t="s">
-        <v>21</v>
-      </c>
-      <c r="C65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65">
-        <v>122</v>
-      </c>
-      <c r="E65">
-        <v>50</v>
-      </c>
-      <c r="F65" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>2025</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64">
+        <v>56150</v>
+      </c>
+      <c r="E64">
+        <v>16.48638808634581</v>
+      </c>
+      <c r="F64" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1796,19 +1771,39 @@
         <v>2025</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D66">
-        <v>122</v>
+        <v>3358</v>
       </c>
       <c r="E66">
-        <v>50</v>
+        <v>26.65079365079365</v>
       </c>
       <c r="F66" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>2025</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67">
+        <v>3312</v>
+      </c>
+      <c r="E67">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="F67" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1816,19 +1811,19 @@
         <v>2025</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D68">
-        <v>2085</v>
+        <v>2979</v>
       </c>
       <c r="E68">
-        <v>28.31726198560369</v>
+        <v>23.64285714285714</v>
       </c>
       <c r="F68" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -1836,39 +1831,19 @@
         <v>2025</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D69">
-        <v>1975</v>
+        <v>2951</v>
       </c>
       <c r="E69">
-        <v>26.82330571777808</v>
+        <v>23.42063492063492</v>
       </c>
       <c r="F69" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>2025</v>
-      </c>
-      <c r="B70" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" t="s">
-        <v>89</v>
-      </c>
-      <c r="D70">
-        <v>1703</v>
-      </c>
-      <c r="E70">
-        <v>23.12915931006383</v>
-      </c>
-      <c r="F70" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -1876,19 +1851,39 @@
         <v>2025</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D71">
-        <v>1600</v>
+        <v>456</v>
       </c>
       <c r="E71">
-        <v>21.73027298655439</v>
+        <v>45.69138276553106</v>
       </c>
       <c r="F71" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>2025</v>
+      </c>
+      <c r="B72" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72">
+        <v>295</v>
+      </c>
+      <c r="E72">
+        <v>29.55911823647295</v>
+      </c>
+      <c r="F72" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -1896,39 +1891,19 @@
         <v>2025</v>
       </c>
       <c r="B73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D73">
-        <v>119488</v>
+        <v>247</v>
       </c>
       <c r="E73">
-        <v>35.08326873840227</v>
+        <v>24.74949899799599</v>
       </c>
       <c r="F73" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>2025</v>
-      </c>
-      <c r="B74" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" t="s">
-        <v>92</v>
-      </c>
-      <c r="D74">
-        <v>107081</v>
-      </c>
-      <c r="E74">
-        <v>31.4404082399643</v>
-      </c>
-      <c r="F74" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -1936,19 +1911,19 @@
         <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D75">
-        <v>57865</v>
+        <v>1632</v>
       </c>
       <c r="E75">
-        <v>16.98993493528762</v>
+        <v>48.83303411131059</v>
       </c>
       <c r="F75" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -1956,39 +1931,39 @@
         <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D76">
-        <v>56150</v>
+        <v>1333</v>
       </c>
       <c r="E76">
-        <v>16.48638808634581</v>
+        <v>39.88629563135847</v>
       </c>
       <c r="F76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>2025</v>
-      </c>
-      <c r="B78" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78">
-        <v>3358</v>
-      </c>
-      <c r="E78">
-        <v>26.65079365079365</v>
-      </c>
-      <c r="F78" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>2025</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" t="s">
+        <v>91</v>
+      </c>
+      <c r="D77">
+        <v>377</v>
+      </c>
+      <c r="E77">
+        <v>11.28067025733094</v>
+      </c>
+      <c r="F77" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -1996,19 +1971,19 @@
         <v>2025</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D79">
-        <v>3312</v>
+        <v>5569</v>
       </c>
       <c r="E79">
-        <v>26.28571428571428</v>
+        <v>28.0102605371693</v>
       </c>
       <c r="F79" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2016,19 +1991,19 @@
         <v>2025</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D80">
-        <v>2979</v>
+        <v>5388</v>
       </c>
       <c r="E80">
-        <v>23.64285714285714</v>
+        <v>27.09988934714818</v>
       </c>
       <c r="F80" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2036,39 +2011,39 @@
         <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D81">
-        <v>2951</v>
+        <v>4501</v>
       </c>
       <c r="E81">
-        <v>23.42063492063492</v>
+        <v>22.63856754853636</v>
       </c>
       <c r="F81" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>2025</v>
-      </c>
-      <c r="B83" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" t="s">
-        <v>99</v>
-      </c>
-      <c r="D83">
-        <v>456</v>
-      </c>
-      <c r="E83">
-        <v>45.69138276553106</v>
-      </c>
-      <c r="F83" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>2025</v>
+      </c>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82">
+        <v>4424</v>
+      </c>
+      <c r="E82">
+        <v>22.25128256714616</v>
+      </c>
+      <c r="F82" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2076,19 +2051,19 @@
         <v>2025</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D84">
-        <v>295</v>
+        <v>2305</v>
       </c>
       <c r="E84">
-        <v>29.55911823647295</v>
+        <v>41.33787661406026</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2096,39 +2071,39 @@
         <v>2025</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D85">
-        <v>247</v>
+        <v>1847</v>
       </c>
       <c r="E85">
-        <v>24.74949899799599</v>
+        <v>33.12410329985653</v>
       </c>
       <c r="F85" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>2025</v>
-      </c>
-      <c r="B87" t="s">
-        <v>26</v>
-      </c>
-      <c r="C87" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87">
-        <v>148</v>
-      </c>
-      <c r="E87">
-        <v>50</v>
-      </c>
-      <c r="F87" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>2025</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D86">
+        <v>1424</v>
+      </c>
+      <c r="E86">
+        <v>25.53802008608321</v>
+      </c>
+      <c r="F86" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2136,19 +2111,39 @@
         <v>2025</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D88">
-        <v>148</v>
+        <v>2731</v>
       </c>
       <c r="E88">
-        <v>50</v>
+        <v>26.66731764476125</v>
       </c>
       <c r="F88" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>2025</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89">
+        <v>2689</v>
+      </c>
+      <c r="E89">
+        <v>26.25720144517137</v>
+      </c>
+      <c r="F89" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2156,19 +2151,19 @@
         <v>2025</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D90">
-        <v>1632</v>
+        <v>2447</v>
       </c>
       <c r="E90">
-        <v>48.83303411131059</v>
+        <v>23.89415096182013</v>
       </c>
       <c r="F90" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2176,39 +2171,39 @@
         <v>2025</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D91">
-        <v>1333</v>
+        <v>2374</v>
       </c>
       <c r="E91">
-        <v>39.88629563135847</v>
+        <v>23.18132994824724</v>
       </c>
       <c r="F91" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>2025</v>
-      </c>
-      <c r="B92" t="s">
-        <v>27</v>
-      </c>
-      <c r="C92" t="s">
-        <v>106</v>
-      </c>
-      <c r="D92">
-        <v>377</v>
-      </c>
-      <c r="E92">
-        <v>11.28067025733094</v>
-      </c>
-      <c r="F92" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>2025</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93">
+        <v>3334</v>
+      </c>
+      <c r="E93">
+        <v>33.58178887993554</v>
+      </c>
+      <c r="F93" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2216,19 +2211,19 @@
         <v>2025</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D94">
-        <v>5569</v>
+        <v>3330</v>
       </c>
       <c r="E94">
-        <v>28.0102605371693</v>
+        <v>33.54149879129734</v>
       </c>
       <c r="F94" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2236,39 +2231,19 @@
         <v>2025</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D95">
-        <v>5388</v>
+        <v>3264</v>
       </c>
       <c r="E95">
-        <v>27.09988934714818</v>
+        <v>32.87671232876712</v>
       </c>
       <c r="F95" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>2025</v>
-      </c>
-      <c r="B96" t="s">
-        <v>28</v>
-      </c>
-      <c r="C96" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96">
-        <v>4501</v>
-      </c>
-      <c r="E96">
-        <v>22.63856754853636</v>
-      </c>
-      <c r="F96" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2276,19 +2251,39 @@
         <v>2025</v>
       </c>
       <c r="B97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D97">
-        <v>4424</v>
+        <v>3997</v>
       </c>
       <c r="E97">
-        <v>22.25128256714616</v>
+        <v>29.58768228588349</v>
       </c>
       <c r="F97" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>2025</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98">
+        <v>3483</v>
+      </c>
+      <c r="E98">
+        <v>25.78281145902731</v>
+      </c>
+      <c r="F98" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2296,19 +2291,19 @@
         <v>2025</v>
       </c>
       <c r="B99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D99">
-        <v>2305</v>
+        <v>3157</v>
       </c>
       <c r="E99">
-        <v>41.33787661406026</v>
+        <v>23.3696054482197</v>
       </c>
       <c r="F99" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2316,39 +2311,39 @@
         <v>2025</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D100">
-        <v>1847</v>
+        <v>2872</v>
       </c>
       <c r="E100">
-        <v>33.12410329985653</v>
+        <v>21.2599008068695</v>
       </c>
       <c r="F100" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>2025</v>
-      </c>
-      <c r="B101" t="s">
-        <v>29</v>
-      </c>
-      <c r="C101" t="s">
-        <v>113</v>
-      </c>
-      <c r="D101">
-        <v>1424</v>
-      </c>
-      <c r="E101">
-        <v>25.53802008608321</v>
-      </c>
-      <c r="F101" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>2025</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" t="s">
+        <v>110</v>
+      </c>
+      <c r="D102">
+        <v>1422</v>
+      </c>
+      <c r="E102">
+        <v>49.1701244813278</v>
+      </c>
+      <c r="F102" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2356,19 +2351,19 @@
         <v>2025</v>
       </c>
       <c r="B103" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D103">
-        <v>2731</v>
+        <v>1409</v>
       </c>
       <c r="E103">
-        <v>26.66731764476125</v>
+        <v>48.72060857538036</v>
       </c>
       <c r="F103" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2376,39 +2371,19 @@
         <v>2025</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D104">
-        <v>2689</v>
+        <v>53</v>
       </c>
       <c r="E104">
-        <v>26.25720144517137</v>
+        <v>1.832641770401107</v>
       </c>
       <c r="F104" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>2025</v>
-      </c>
-      <c r="B105" t="s">
-        <v>30</v>
-      </c>
-      <c r="C105" t="s">
-        <v>116</v>
-      </c>
-      <c r="D105">
-        <v>2447</v>
-      </c>
-      <c r="E105">
-        <v>23.89415096182013</v>
-      </c>
-      <c r="F105" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2416,19 +2391,39 @@
         <v>2025</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C106" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D106">
-        <v>2374</v>
+        <v>532</v>
       </c>
       <c r="E106">
-        <v>23.18132994824724</v>
+        <v>43.53518821603928</v>
       </c>
       <c r="F106" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107">
+        <v>2025</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107">
+        <v>398</v>
+      </c>
+      <c r="E107">
+        <v>32.56955810147299</v>
+      </c>
+      <c r="F107" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -2436,39 +2431,19 @@
         <v>2025</v>
       </c>
       <c r="B108" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C108" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D108">
-        <v>3334</v>
+        <v>292</v>
       </c>
       <c r="E108">
-        <v>33.58178887993554</v>
+        <v>23.89525368248772</v>
       </c>
       <c r="F108" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>2025</v>
-      </c>
-      <c r="B109" t="s">
-        <v>31</v>
-      </c>
-      <c r="C109" t="s">
-        <v>119</v>
-      </c>
-      <c r="D109">
-        <v>3330</v>
-      </c>
-      <c r="E109">
-        <v>33.54149879129734</v>
-      </c>
-      <c r="F109" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2476,19 +2451,39 @@
         <v>2025</v>
       </c>
       <c r="B110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D110">
-        <v>3264</v>
+        <v>22220</v>
       </c>
       <c r="E110">
-        <v>32.87671232876712</v>
+        <v>31.99838712000115</v>
       </c>
       <c r="F110" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
+        <v>2025</v>
+      </c>
+      <c r="B111" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" t="s">
+        <v>117</v>
+      </c>
+      <c r="D111">
+        <v>17953</v>
+      </c>
+      <c r="E111">
+        <v>25.853602338676</v>
+      </c>
+      <c r="F111" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2496,19 +2491,19 @@
         <v>2025</v>
       </c>
       <c r="B112" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C112" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D112">
-        <v>3997</v>
+        <v>16959</v>
       </c>
       <c r="E112">
-        <v>29.58768228588349</v>
+        <v>24.42217133969845</v>
       </c>
       <c r="F112" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -2516,39 +2511,19 @@
         <v>2025</v>
       </c>
       <c r="B113" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C113" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D113">
-        <v>3483</v>
+        <v>12309</v>
       </c>
       <c r="E113">
-        <v>25.78281145902731</v>
+        <v>17.7258392016244</v>
       </c>
       <c r="F113" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>2025</v>
-      </c>
-      <c r="B114" t="s">
-        <v>32</v>
-      </c>
-      <c r="C114" t="s">
-        <v>123</v>
-      </c>
-      <c r="D114">
-        <v>3157</v>
-      </c>
-      <c r="E114">
-        <v>23.3696054482197</v>
-      </c>
-      <c r="F114" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -2556,19 +2531,39 @@
         <v>2025</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C115" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D115">
-        <v>2872</v>
+        <v>884</v>
       </c>
       <c r="E115">
-        <v>21.2599008068695</v>
+        <v>40.38373686614893</v>
       </c>
       <c r="F115" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
+        <v>2025</v>
+      </c>
+      <c r="B116" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" t="s">
+        <v>121</v>
+      </c>
+      <c r="D116">
+        <v>716</v>
+      </c>
+      <c r="E116">
+        <v>32.7089995431704</v>
+      </c>
+      <c r="F116" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2576,259 +2571,19 @@
         <v>2025</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C117" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D117">
-        <v>1422</v>
+        <v>589</v>
       </c>
       <c r="E117">
-        <v>49.1701244813278</v>
+        <v>26.90726359068067</v>
       </c>
       <c r="F117" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>2025</v>
-      </c>
-      <c r="B118" t="s">
-        <v>33</v>
-      </c>
-      <c r="C118" t="s">
-        <v>126</v>
-      </c>
-      <c r="D118">
-        <v>1409</v>
-      </c>
-      <c r="E118">
-        <v>48.72060857538036</v>
-      </c>
-      <c r="F118" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>2025</v>
-      </c>
-      <c r="B119" t="s">
-        <v>33</v>
-      </c>
-      <c r="C119" t="s">
-        <v>127</v>
-      </c>
-      <c r="D119">
-        <v>53</v>
-      </c>
-      <c r="E119">
-        <v>1.832641770401107</v>
-      </c>
-      <c r="F119" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>2025</v>
-      </c>
-      <c r="B121" t="s">
-        <v>34</v>
-      </c>
-      <c r="C121" t="s">
-        <v>128</v>
-      </c>
-      <c r="D121">
-        <v>532</v>
-      </c>
-      <c r="E121">
-        <v>43.53518821603928</v>
-      </c>
-      <c r="F121" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>2025</v>
-      </c>
-      <c r="B122" t="s">
-        <v>34</v>
-      </c>
-      <c r="C122" t="s">
-        <v>129</v>
-      </c>
-      <c r="D122">
-        <v>398</v>
-      </c>
-      <c r="E122">
-        <v>32.56955810147299</v>
-      </c>
-      <c r="F122" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>2025</v>
-      </c>
-      <c r="B123" t="s">
-        <v>34</v>
-      </c>
-      <c r="C123" t="s">
-        <v>130</v>
-      </c>
-      <c r="D123">
-        <v>292</v>
-      </c>
-      <c r="E123">
-        <v>23.89525368248772</v>
-      </c>
-      <c r="F123" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>2025</v>
-      </c>
-      <c r="B125" t="s">
-        <v>35</v>
-      </c>
-      <c r="C125" t="s">
-        <v>131</v>
-      </c>
-      <c r="D125">
-        <v>22220</v>
-      </c>
-      <c r="E125">
-        <v>31.99838712000115</v>
-      </c>
-      <c r="F125" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>2025</v>
-      </c>
-      <c r="B126" t="s">
-        <v>35</v>
-      </c>
-      <c r="C126" t="s">
-        <v>132</v>
-      </c>
-      <c r="D126">
-        <v>17953</v>
-      </c>
-      <c r="E126">
-        <v>25.853602338676</v>
-      </c>
-      <c r="F126" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>2025</v>
-      </c>
-      <c r="B127" t="s">
-        <v>35</v>
-      </c>
-      <c r="C127" t="s">
-        <v>133</v>
-      </c>
-      <c r="D127">
-        <v>16959</v>
-      </c>
-      <c r="E127">
-        <v>24.42217133969845</v>
-      </c>
-      <c r="F127" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>2025</v>
-      </c>
-      <c r="B128" t="s">
-        <v>35</v>
-      </c>
-      <c r="C128" t="s">
-        <v>134</v>
-      </c>
-      <c r="D128">
-        <v>12309</v>
-      </c>
-      <c r="E128">
-        <v>17.7258392016244</v>
-      </c>
-      <c r="F128" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>2025</v>
-      </c>
-      <c r="B130" t="s">
-        <v>36</v>
-      </c>
-      <c r="C130" t="s">
-        <v>135</v>
-      </c>
-      <c r="D130">
-        <v>884</v>
-      </c>
-      <c r="E130">
-        <v>40.38373686614893</v>
-      </c>
-      <c r="F130" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>2025</v>
-      </c>
-      <c r="B131" t="s">
-        <v>36</v>
-      </c>
-      <c r="C131" t="s">
-        <v>136</v>
-      </c>
-      <c r="D131">
-        <v>716</v>
-      </c>
-      <c r="E131">
-        <v>32.7089995431704</v>
-      </c>
-      <c r="F131" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>2025</v>
-      </c>
-      <c r="B132" t="s">
-        <v>36</v>
-      </c>
-      <c r="C132" t="s">
-        <v>137</v>
-      </c>
-      <c r="D132">
-        <v>589</v>
-      </c>
-      <c r="E132">
-        <v>26.90726359068067</v>
-      </c>
-      <c r="F132" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
